--- a/louvain_baseline_experiments/louvain_Baseline_ucidata-zachary_normalized/louvain_Baseline_ucidata-zachary_normalized_results.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_ucidata-zachary_normalized/louvain_Baseline_ucidata-zachary_normalized_results.xlsx
@@ -550,13 +550,13 @@
         <v>0.4197896120973044</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001372099999571219</v>
+        <v>0.001378099999783444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003757899998163339</v>
+        <v>0.003924799999367679</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08097080000152346</v>
+        <v>0.1005603000012343</v>
       </c>
     </row>
   </sheetData>
